--- a/student_enrollment_forms/029_student_loan_assistance_request_form--student_enrollment_forms.xlsx
+++ b/student_enrollment_forms/029_student_loan_assistance_request_form--student_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time_student'}</t>
+          <t>full-time_student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-time Student'}</t>
+          <t>Full-time Student</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part-time_student'}</t>
+          <t>part-time_student</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part-time Student'}</t>
+          <t>Part-time Student</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'federal'}</t>
+          <t>federal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Federal'}</t>
+          <t>Federal</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-loan_default'}</t>
+          <t>in-loan_default</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-Loan Default'}</t>
+          <t>In-Loan Default</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'standard_repayment'}</t>
+          <t>standard_repayment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Standard Repayment'}</t>
+          <t>Standard Repayment</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'income-driven_repayment'}</t>
+          <t>income-driven_repayment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Income-Driven Repayment'}</t>
+          <t>Income-Driven Repayment</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pay-as-you-go'}</t>
+          <t>pay-as-you-go</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pay-As-You-Go'}</t>
+          <t>Pay-As-You-Go</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'public_service_loan_forgiveness'}</t>
+          <t>public_service_loan_forgiveness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Public Service Loan Forgiveness'}</t>
+          <t>Public Service Loan Forgiveness</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'deferment'}</t>
+          <t>deferment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Deferment'}</t>
+          <t>Deferment</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'forbearance'}</t>
+          <t>forbearance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Forbearance'}</t>
+          <t>Forbearance</t>
         </is>
       </c>
     </row>
